--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405755</v>
+        <v>113405738</v>
       </c>
       <c r="B7" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296807</v>
+        <v>296551</v>
       </c>
       <c r="R7" t="n">
-        <v>6530177</v>
+        <v>6530280</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405738</v>
+        <v>113405755</v>
       </c>
       <c r="B8" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,16 +1323,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296551</v>
+        <v>296807</v>
       </c>
       <c r="R8" t="n">
-        <v>6530280</v>
+        <v>6530177</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405754</v>
+        <v>113405757</v>
       </c>
       <c r="B11" t="n">
         <v>56781</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296674</v>
+        <v>296724</v>
       </c>
       <c r="R11" t="n">
-        <v>6530109</v>
+        <v>6530086</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405757</v>
+        <v>113405754</v>
       </c>
       <c r="B12" t="n">
         <v>56781</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296724</v>
+        <v>296674</v>
       </c>
       <c r="R12" t="n">
-        <v>6530086</v>
+        <v>6530109</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405747</v>
+        <v>113405744</v>
       </c>
       <c r="B20" t="n">
         <v>56765</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296643</v>
+        <v>296637</v>
       </c>
       <c r="R20" t="n">
-        <v>6530110</v>
+        <v>6530116</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405744</v>
+        <v>113405747</v>
       </c>
       <c r="B21" t="n">
         <v>56765</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296637</v>
+        <v>296643</v>
       </c>
       <c r="R21" t="n">
-        <v>6530116</v>
+        <v>6530110</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113405737</v>
       </c>
       <c r="B2" t="n">
-        <v>93739</v>
+        <v>93755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405740</v>
+        <v>113405738</v>
       </c>
       <c r="B3" t="n">
         <v>56765</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296642</v>
+        <v>296551</v>
       </c>
       <c r="R3" t="n">
-        <v>6530112</v>
+        <v>6530280</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405745</v>
+        <v>113405756</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,16 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296589</v>
+        <v>296720</v>
       </c>
       <c r="R4" t="n">
-        <v>6530303</v>
+        <v>6530093</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405750</v>
+        <v>113405757</v>
       </c>
       <c r="B5" t="n">
         <v>56781</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296573</v>
+        <v>296724</v>
       </c>
       <c r="R5" t="n">
-        <v>6530298</v>
+        <v>6530086</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405761</v>
+        <v>113405759</v>
       </c>
       <c r="B6" t="n">
-        <v>96261</v>
+        <v>56781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296536</v>
+        <v>296634</v>
       </c>
       <c r="R6" t="n">
-        <v>6530289</v>
+        <v>6530176</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405738</v>
+        <v>113405761</v>
       </c>
       <c r="B7" t="n">
-        <v>56765</v>
+        <v>96277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296551</v>
+        <v>296536</v>
       </c>
       <c r="R7" t="n">
-        <v>6530280</v>
+        <v>6530289</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405755</v>
+        <v>113405743</v>
       </c>
       <c r="B8" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,16 +1323,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296807</v>
+        <v>296578</v>
       </c>
       <c r="R8" t="n">
-        <v>6530177</v>
+        <v>6530336</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405753</v>
+        <v>113405741</v>
       </c>
       <c r="B9" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296642</v>
+        <v>296641</v>
       </c>
       <c r="R9" t="n">
-        <v>6530097</v>
+        <v>6530111</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405742</v>
+        <v>113405751</v>
       </c>
       <c r="B10" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296646</v>
+        <v>296671</v>
       </c>
       <c r="R10" t="n">
-        <v>6530116</v>
+        <v>6530142</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405757</v>
+        <v>113405755</v>
       </c>
       <c r="B11" t="n">
         <v>56781</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296724</v>
+        <v>296807</v>
       </c>
       <c r="R11" t="n">
-        <v>6530086</v>
+        <v>6530177</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405749</v>
+        <v>113405742</v>
       </c>
       <c r="B13" t="n">
-        <v>56910</v>
+        <v>56765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296716</v>
+        <v>296646</v>
       </c>
       <c r="R13" t="n">
-        <v>6530077</v>
+        <v>6530116</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1918,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405752</v>
+        <v>113405753</v>
       </c>
       <c r="B14" t="n">
         <v>56781</v>
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296684</v>
+        <v>296642</v>
       </c>
       <c r="R14" t="n">
-        <v>6530120</v>
+        <v>6530097</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2051,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405758</v>
+        <v>113405744</v>
       </c>
       <c r="B15" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,16 +2072,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296587</v>
+        <v>296637</v>
       </c>
       <c r="R15" t="n">
-        <v>6530221</v>
+        <v>6530116</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2131,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405759</v>
+        <v>113405752</v>
       </c>
       <c r="B16" t="n">
         <v>56781</v>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296634</v>
+        <v>296684</v>
       </c>
       <c r="R16" t="n">
-        <v>6530176</v>
+        <v>6530120</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2238,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405741</v>
+        <v>113405740</v>
       </c>
       <c r="B17" t="n">
         <v>56765</v>
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296641</v>
+        <v>296642</v>
       </c>
       <c r="R17" t="n">
-        <v>6530111</v>
+        <v>6530112</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2372,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405739</v>
+        <v>113405749</v>
       </c>
       <c r="B18" t="n">
-        <v>56765</v>
+        <v>56910</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296794</v>
+        <v>296716</v>
       </c>
       <c r="R18" t="n">
-        <v>6530160</v>
+        <v>6530077</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2448,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405743</v>
+        <v>113405758</v>
       </c>
       <c r="B19" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296578</v>
+        <v>296587</v>
       </c>
       <c r="R19" t="n">
-        <v>6530336</v>
+        <v>6530221</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405744</v>
+        <v>113405747</v>
       </c>
       <c r="B20" t="n">
         <v>56765</v>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296637</v>
+        <v>296643</v>
       </c>
       <c r="R20" t="n">
-        <v>6530116</v>
+        <v>6530110</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405747</v>
+        <v>113405750</v>
       </c>
       <c r="B21" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296643</v>
+        <v>296573</v>
       </c>
       <c r="R21" t="n">
-        <v>6530110</v>
+        <v>6530298</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405751</v>
+        <v>113405745</v>
       </c>
       <c r="B22" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296671</v>
+        <v>296589</v>
       </c>
       <c r="R22" t="n">
-        <v>6530142</v>
+        <v>6530303</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405756</v>
+        <v>113405739</v>
       </c>
       <c r="B23" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,16 +2923,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296720</v>
+        <v>296794</v>
       </c>
       <c r="R23" t="n">
-        <v>6530093</v>
+        <v>6530160</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405737</v>
+        <v>113405738</v>
       </c>
       <c r="B2" t="n">
-        <v>93755</v>
+        <v>56765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296703</v>
+        <v>296551</v>
       </c>
       <c r="R2" t="n">
-        <v>6530117</v>
+        <v>6530280</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405738</v>
+        <v>113405737</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>93755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296551</v>
+        <v>296703</v>
       </c>
       <c r="R3" t="n">
-        <v>6530280</v>
+        <v>6530117</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405738</v>
+        <v>113405749</v>
       </c>
       <c r="B2" t="n">
-        <v>56765</v>
+        <v>56910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296551</v>
+        <v>296716</v>
       </c>
       <c r="R2" t="n">
-        <v>6530280</v>
+        <v>6530077</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405737</v>
+        <v>113405753</v>
       </c>
       <c r="B3" t="n">
-        <v>93755</v>
+        <v>56781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296703</v>
+        <v>296642</v>
       </c>
       <c r="R3" t="n">
-        <v>6530117</v>
+        <v>6530097</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405756</v>
+        <v>113405742</v>
       </c>
       <c r="B4" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,16 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296720</v>
+        <v>296646</v>
       </c>
       <c r="R4" t="n">
-        <v>6530093</v>
+        <v>6530116</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405757</v>
+        <v>113405743</v>
       </c>
       <c r="B5" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296724</v>
+        <v>296578</v>
       </c>
       <c r="R5" t="n">
-        <v>6530086</v>
+        <v>6530336</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405759</v>
+        <v>113405738</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,16 +1114,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296634</v>
+        <v>296551</v>
       </c>
       <c r="R6" t="n">
-        <v>6530176</v>
+        <v>6530280</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405743</v>
+        <v>113405757</v>
       </c>
       <c r="B8" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,16 +1323,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296578</v>
+        <v>296724</v>
       </c>
       <c r="R8" t="n">
-        <v>6530336</v>
+        <v>6530086</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405751</v>
+        <v>113405747</v>
       </c>
       <c r="B10" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296671</v>
+        <v>296643</v>
       </c>
       <c r="R10" t="n">
-        <v>6530142</v>
+        <v>6530110</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405754</v>
+        <v>113405758</v>
       </c>
       <c r="B12" t="n">
         <v>56781</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296674</v>
+        <v>296587</v>
       </c>
       <c r="R12" t="n">
-        <v>6530109</v>
+        <v>6530221</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405742</v>
+        <v>113405756</v>
       </c>
       <c r="B13" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296646</v>
+        <v>296720</v>
       </c>
       <c r="R13" t="n">
-        <v>6530116</v>
+        <v>6530093</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405753</v>
+        <v>113405740</v>
       </c>
       <c r="B14" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1992,7 +1992,7 @@
         <v>296642</v>
       </c>
       <c r="R14" t="n">
-        <v>6530097</v>
+        <v>6530112</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405744</v>
+        <v>113405750</v>
       </c>
       <c r="B15" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296637</v>
+        <v>296573</v>
       </c>
       <c r="R15" t="n">
-        <v>6530116</v>
+        <v>6530298</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405752</v>
+        <v>113405739</v>
       </c>
       <c r="B16" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296684</v>
+        <v>296794</v>
       </c>
       <c r="R16" t="n">
-        <v>6530120</v>
+        <v>6530160</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405740</v>
+        <v>113405737</v>
       </c>
       <c r="B17" t="n">
-        <v>56765</v>
+        <v>93755</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296642</v>
+        <v>296703</v>
       </c>
       <c r="R17" t="n">
-        <v>6530112</v>
+        <v>6530117</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2346,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405749</v>
+        <v>113405752</v>
       </c>
       <c r="B18" t="n">
-        <v>56910</v>
+        <v>56781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296716</v>
+        <v>296684</v>
       </c>
       <c r="R18" t="n">
-        <v>6530077</v>
+        <v>6530120</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2453,6 +2448,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405758</v>
+        <v>113405745</v>
       </c>
       <c r="B19" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296587</v>
+        <v>296589</v>
       </c>
       <c r="R19" t="n">
-        <v>6530221</v>
+        <v>6530303</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405747</v>
+        <v>113405754</v>
       </c>
       <c r="B20" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296643</v>
+        <v>296674</v>
       </c>
       <c r="R20" t="n">
-        <v>6530110</v>
+        <v>6530109</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405750</v>
+        <v>113405759</v>
       </c>
       <c r="B21" t="n">
         <v>56781</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296573</v>
+        <v>296634</v>
       </c>
       <c r="R21" t="n">
-        <v>6530298</v>
+        <v>6530176</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405745</v>
+        <v>113405744</v>
       </c>
       <c r="B22" t="n">
         <v>56765</v>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296589</v>
+        <v>296637</v>
       </c>
       <c r="R22" t="n">
-        <v>6530303</v>
+        <v>6530116</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405739</v>
+        <v>113405751</v>
       </c>
       <c r="B23" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,16 +2923,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296794</v>
+        <v>296671</v>
       </c>
       <c r="R23" t="n">
-        <v>6530160</v>
+        <v>6530142</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405749</v>
+        <v>113405747</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
+        <v>56766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296716</v>
+        <v>296643</v>
       </c>
       <c r="R2" t="n">
-        <v>6530077</v>
+        <v>6530110</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405753</v>
+        <v>113405755</v>
       </c>
       <c r="B3" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296642</v>
+        <v>296807</v>
       </c>
       <c r="R3" t="n">
-        <v>6530097</v>
+        <v>6530177</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405742</v>
+        <v>113405751</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296646</v>
+        <v>296671</v>
       </c>
       <c r="R4" t="n">
-        <v>6530116</v>
+        <v>6530142</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405743</v>
+        <v>113405742</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296578</v>
+        <v>296646</v>
       </c>
       <c r="R5" t="n">
-        <v>6530336</v>
+        <v>6530116</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405738</v>
+        <v>113405744</v>
       </c>
       <c r="B6" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296551</v>
+        <v>296637</v>
       </c>
       <c r="R6" t="n">
-        <v>6530280</v>
+        <v>6530116</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1213,7 @@
         <v>113405761</v>
       </c>
       <c r="B7" t="n">
-        <v>96277</v>
+        <v>96289</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405757</v>
+        <v>113405753</v>
       </c>
       <c r="B8" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296724</v>
+        <v>296642</v>
       </c>
       <c r="R8" t="n">
-        <v>6530086</v>
+        <v>6530097</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405741</v>
+        <v>113405738</v>
       </c>
       <c r="B9" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296641</v>
+        <v>296551</v>
       </c>
       <c r="R9" t="n">
-        <v>6530111</v>
+        <v>6530280</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405747</v>
+        <v>113405737</v>
       </c>
       <c r="B10" t="n">
-        <v>56765</v>
+        <v>93767</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1538,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296643</v>
+        <v>296703</v>
       </c>
       <c r="R10" t="n">
-        <v>6530110</v>
+        <v>6530117</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405755</v>
+        <v>113405741</v>
       </c>
       <c r="B11" t="n">
-        <v>56781</v>
+        <v>56766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296807</v>
+        <v>296641</v>
       </c>
       <c r="R11" t="n">
-        <v>6530177</v>
+        <v>6530111</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405758</v>
+        <v>113405757</v>
       </c>
       <c r="B12" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296587</v>
+        <v>296724</v>
       </c>
       <c r="R12" t="n">
-        <v>6530221</v>
+        <v>6530086</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405756</v>
+        <v>113405749</v>
       </c>
       <c r="B13" t="n">
-        <v>56781</v>
+        <v>56911</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296720</v>
+        <v>296716</v>
       </c>
       <c r="R13" t="n">
-        <v>6530093</v>
+        <v>6530077</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1918,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405740</v>
+        <v>113405756</v>
       </c>
       <c r="B14" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1960,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296642</v>
+        <v>296720</v>
       </c>
       <c r="R14" t="n">
-        <v>6530112</v>
+        <v>6530093</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2029,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405750</v>
+        <v>113405743</v>
       </c>
       <c r="B15" t="n">
-        <v>56781</v>
+        <v>56766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,16 +2067,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296573</v>
+        <v>296578</v>
       </c>
       <c r="R15" t="n">
-        <v>6530298</v>
+        <v>6530336</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405739</v>
+        <v>113405752</v>
       </c>
       <c r="B16" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2174,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296794</v>
+        <v>296684</v>
       </c>
       <c r="R16" t="n">
-        <v>6530160</v>
+        <v>6530120</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2243,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405737</v>
+        <v>113405745</v>
       </c>
       <c r="B17" t="n">
-        <v>93755</v>
+        <v>56766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296703</v>
+        <v>296589</v>
       </c>
       <c r="R17" t="n">
-        <v>6530117</v>
+        <v>6530303</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2346,6 +2341,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405752</v>
+        <v>113405754</v>
       </c>
       <c r="B18" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296684</v>
+        <v>296674</v>
       </c>
       <c r="R18" t="n">
-        <v>6530120</v>
+        <v>6530109</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405745</v>
+        <v>113405759</v>
       </c>
       <c r="B19" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296589</v>
+        <v>296634</v>
       </c>
       <c r="R19" t="n">
-        <v>6530303</v>
+        <v>6530176</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405754</v>
+        <v>113405750</v>
       </c>
       <c r="B20" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296674</v>
+        <v>296573</v>
       </c>
       <c r="R20" t="n">
-        <v>6530109</v>
+        <v>6530298</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405759</v>
+        <v>113405739</v>
       </c>
       <c r="B21" t="n">
-        <v>56781</v>
+        <v>56766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296634</v>
+        <v>296794</v>
       </c>
       <c r="R21" t="n">
-        <v>6530176</v>
+        <v>6530160</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405744</v>
+        <v>113405758</v>
       </c>
       <c r="B22" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296637</v>
+        <v>296587</v>
       </c>
       <c r="R22" t="n">
-        <v>6530116</v>
+        <v>6530221</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405751</v>
+        <v>113405740</v>
       </c>
       <c r="B23" t="n">
-        <v>56781</v>
+        <v>56766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,16 +2923,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296671</v>
+        <v>296642</v>
       </c>
       <c r="R23" t="n">
-        <v>6530142</v>
+        <v>6530112</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405747</v>
+        <v>113405752</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296643</v>
+        <v>296684</v>
       </c>
       <c r="R2" t="n">
-        <v>6530110</v>
+        <v>6530120</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405755</v>
+        <v>113405754</v>
       </c>
       <c r="B3" t="n">
         <v>56782</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296807</v>
+        <v>296674</v>
       </c>
       <c r="R3" t="n">
-        <v>6530177</v>
+        <v>6530109</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405751</v>
+        <v>113405759</v>
       </c>
       <c r="B4" t="n">
         <v>56782</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296671</v>
+        <v>296634</v>
       </c>
       <c r="R4" t="n">
-        <v>6530142</v>
+        <v>6530176</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405744</v>
+        <v>113405749</v>
       </c>
       <c r="B6" t="n">
-        <v>56766</v>
+        <v>56911</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296637</v>
+        <v>296716</v>
       </c>
       <c r="R6" t="n">
-        <v>6530116</v>
+        <v>6530077</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405761</v>
+        <v>113405755</v>
       </c>
       <c r="B7" t="n">
-        <v>96289</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296536</v>
+        <v>296807</v>
       </c>
       <c r="R7" t="n">
-        <v>6530289</v>
+        <v>6530177</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405753</v>
+        <v>113405751</v>
       </c>
       <c r="B8" t="n">
         <v>56782</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296642</v>
+        <v>296671</v>
       </c>
       <c r="R8" t="n">
-        <v>6530097</v>
+        <v>6530142</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405738</v>
+        <v>113405743</v>
       </c>
       <c r="B9" t="n">
         <v>56766</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296551</v>
+        <v>296578</v>
       </c>
       <c r="R9" t="n">
-        <v>6530280</v>
+        <v>6530336</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405737</v>
+        <v>113405758</v>
       </c>
       <c r="B10" t="n">
-        <v>93767</v>
+        <v>56782</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,25 +1538,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296703</v>
+        <v>296587</v>
       </c>
       <c r="R10" t="n">
-        <v>6530117</v>
+        <v>6530221</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405741</v>
+        <v>113405756</v>
       </c>
       <c r="B11" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,16 +1649,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296641</v>
+        <v>296720</v>
       </c>
       <c r="R11" t="n">
-        <v>6530111</v>
+        <v>6530093</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405757</v>
+        <v>113405761</v>
       </c>
       <c r="B12" t="n">
-        <v>56782</v>
+        <v>96289</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296724</v>
+        <v>296536</v>
       </c>
       <c r="R12" t="n">
-        <v>6530086</v>
+        <v>6530289</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1811,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405749</v>
+        <v>113405738</v>
       </c>
       <c r="B13" t="n">
-        <v>56911</v>
+        <v>56766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296716</v>
+        <v>296551</v>
       </c>
       <c r="R13" t="n">
-        <v>6530077</v>
+        <v>6530280</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1918,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405756</v>
+        <v>113405744</v>
       </c>
       <c r="B14" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296720</v>
+        <v>296637</v>
       </c>
       <c r="R14" t="n">
-        <v>6530093</v>
+        <v>6530116</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2024,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405743</v>
+        <v>113405737</v>
       </c>
       <c r="B15" t="n">
-        <v>56766</v>
+        <v>93767</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,25 +2068,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296578</v>
+        <v>296703</v>
       </c>
       <c r="R15" t="n">
-        <v>6530336</v>
+        <v>6530117</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2127,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405752</v>
+        <v>113405757</v>
       </c>
       <c r="B16" t="n">
         <v>56782</v>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296684</v>
+        <v>296724</v>
       </c>
       <c r="R16" t="n">
-        <v>6530120</v>
+        <v>6530086</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405745</v>
+        <v>113405747</v>
       </c>
       <c r="B17" t="n">
         <v>56766</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296589</v>
+        <v>296643</v>
       </c>
       <c r="R17" t="n">
-        <v>6530303</v>
+        <v>6530110</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405754</v>
+        <v>113405740</v>
       </c>
       <c r="B18" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,16 +2388,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296674</v>
+        <v>296642</v>
       </c>
       <c r="R18" t="n">
-        <v>6530109</v>
+        <v>6530112</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405759</v>
+        <v>113405739</v>
       </c>
       <c r="B19" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296634</v>
+        <v>296794</v>
       </c>
       <c r="R19" t="n">
-        <v>6530176</v>
+        <v>6530160</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405750</v>
+        <v>113405741</v>
       </c>
       <c r="B20" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296573</v>
+        <v>296641</v>
       </c>
       <c r="R20" t="n">
-        <v>6530298</v>
+        <v>6530111</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405739</v>
+        <v>113405750</v>
       </c>
       <c r="B21" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296794</v>
+        <v>296573</v>
       </c>
       <c r="R21" t="n">
-        <v>6530160</v>
+        <v>6530298</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405758</v>
+        <v>113405745</v>
       </c>
       <c r="B22" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296587</v>
+        <v>296589</v>
       </c>
       <c r="R22" t="n">
-        <v>6530221</v>
+        <v>6530303</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405740</v>
+        <v>113405753</v>
       </c>
       <c r="B23" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,16 +2923,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2950,7 +2950,7 @@
         <v>296642</v>
       </c>
       <c r="R23" t="n">
-        <v>6530112</v>
+        <v>6530097</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -2693,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405750</v>
+        <v>113405753</v>
       </c>
       <c r="B21" t="n">
         <v>56782</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296573</v>
+        <v>296642</v>
       </c>
       <c r="R21" t="n">
-        <v>6530298</v>
+        <v>6530097</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405745</v>
+        <v>113405750</v>
       </c>
       <c r="B22" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296589</v>
+        <v>296573</v>
       </c>
       <c r="R22" t="n">
-        <v>6530303</v>
+        <v>6530298</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405753</v>
+        <v>113405745</v>
       </c>
       <c r="B23" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,16 +2923,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296642</v>
+        <v>296589</v>
       </c>
       <c r="R23" t="n">
-        <v>6530097</v>
+        <v>6530303</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405752</v>
+        <v>113405758</v>
       </c>
       <c r="B2" t="n">
         <v>56782</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296684</v>
+        <v>296587</v>
       </c>
       <c r="R2" t="n">
-        <v>6530120</v>
+        <v>6530221</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405759</v>
+        <v>113405755</v>
       </c>
       <c r="B4" t="n">
         <v>56782</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296634</v>
+        <v>296807</v>
       </c>
       <c r="R4" t="n">
-        <v>6530176</v>
+        <v>6530177</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405742</v>
+        <v>113405738</v>
       </c>
       <c r="B5" t="n">
         <v>56766</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296646</v>
+        <v>296551</v>
       </c>
       <c r="R5" t="n">
-        <v>6530116</v>
+        <v>6530280</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405749</v>
+        <v>113405744</v>
       </c>
       <c r="B6" t="n">
-        <v>56911</v>
+        <v>56766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296716</v>
+        <v>296637</v>
       </c>
       <c r="R6" t="n">
-        <v>6530077</v>
+        <v>6530116</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405755</v>
+        <v>113405749</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>56911</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296807</v>
+        <v>296716</v>
       </c>
       <c r="R7" t="n">
-        <v>6530177</v>
+        <v>6530077</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405751</v>
+        <v>113405757</v>
       </c>
       <c r="B8" t="n">
         <v>56782</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296671</v>
+        <v>296724</v>
       </c>
       <c r="R8" t="n">
-        <v>6530142</v>
+        <v>6530086</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405743</v>
+        <v>113405756</v>
       </c>
       <c r="B9" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296578</v>
+        <v>296720</v>
       </c>
       <c r="R9" t="n">
-        <v>6530336</v>
+        <v>6530093</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405758</v>
+        <v>113405742</v>
       </c>
       <c r="B10" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296587</v>
+        <v>296646</v>
       </c>
       <c r="R10" t="n">
-        <v>6530221</v>
+        <v>6530116</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405756</v>
+        <v>113405745</v>
       </c>
       <c r="B11" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,16 +1649,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296720</v>
+        <v>296589</v>
       </c>
       <c r="R11" t="n">
-        <v>6530093</v>
+        <v>6530303</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405761</v>
+        <v>113405743</v>
       </c>
       <c r="B12" t="n">
-        <v>96289</v>
+        <v>56766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296536</v>
+        <v>296578</v>
       </c>
       <c r="R12" t="n">
-        <v>6530289</v>
+        <v>6530336</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1816,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405738</v>
+        <v>113405739</v>
       </c>
       <c r="B13" t="n">
         <v>56766</v>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296551</v>
+        <v>296794</v>
       </c>
       <c r="R13" t="n">
-        <v>6530280</v>
+        <v>6530160</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1949,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405744</v>
+        <v>113405741</v>
       </c>
       <c r="B14" t="n">
         <v>56766</v>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296637</v>
+        <v>296641</v>
       </c>
       <c r="R14" t="n">
-        <v>6530116</v>
+        <v>6530111</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2029,7 +2034,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405737</v>
+        <v>113405747</v>
       </c>
       <c r="B15" t="n">
-        <v>93767</v>
+        <v>56766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,25 +2073,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296703</v>
+        <v>296643</v>
       </c>
       <c r="R15" t="n">
-        <v>6530117</v>
+        <v>6530110</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2132,6 +2137,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405757</v>
+        <v>113405761</v>
       </c>
       <c r="B16" t="n">
-        <v>56782</v>
+        <v>96311</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,25 +2180,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296724</v>
+        <v>296536</v>
       </c>
       <c r="R16" t="n">
-        <v>6530086</v>
+        <v>6530289</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2234,11 +2244,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405747</v>
+        <v>113405753</v>
       </c>
       <c r="B17" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,16 +2286,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296643</v>
+        <v>296642</v>
       </c>
       <c r="R17" t="n">
-        <v>6530110</v>
+        <v>6530097</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2345,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405740</v>
+        <v>113405751</v>
       </c>
       <c r="B18" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,16 +2393,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2412,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296642</v>
+        <v>296671</v>
       </c>
       <c r="R18" t="n">
-        <v>6530112</v>
+        <v>6530142</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405739</v>
+        <v>113405750</v>
       </c>
       <c r="B19" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,16 +2500,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296794</v>
+        <v>296573</v>
       </c>
       <c r="R19" t="n">
-        <v>6530160</v>
+        <v>6530298</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405741</v>
+        <v>113405759</v>
       </c>
       <c r="B20" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,16 +2607,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296641</v>
+        <v>296634</v>
       </c>
       <c r="R20" t="n">
-        <v>6530111</v>
+        <v>6530176</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2666,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405753</v>
+        <v>113405752</v>
       </c>
       <c r="B21" t="n">
         <v>56782</v>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296642</v>
+        <v>296684</v>
       </c>
       <c r="R21" t="n">
-        <v>6530097</v>
+        <v>6530120</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2800,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405750</v>
+        <v>113405740</v>
       </c>
       <c r="B22" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2821,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296573</v>
+        <v>296642</v>
       </c>
       <c r="R22" t="n">
-        <v>6530298</v>
+        <v>6530112</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405745</v>
+        <v>113405737</v>
       </c>
       <c r="B23" t="n">
-        <v>56766</v>
+        <v>93789</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,25 +2924,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296589</v>
+        <v>296703</v>
       </c>
       <c r="R23" t="n">
-        <v>6530303</v>
+        <v>6530117</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2983,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405758</v>
+        <v>113405755</v>
       </c>
       <c r="B2" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296587</v>
+        <v>296807</v>
       </c>
       <c r="R2" t="n">
-        <v>6530221</v>
+        <v>6530177</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405754</v>
+        <v>113405753</v>
       </c>
       <c r="B3" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296674</v>
+        <v>296642</v>
       </c>
       <c r="R3" t="n">
-        <v>6530109</v>
+        <v>6530097</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405755</v>
+        <v>113405752</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296807</v>
+        <v>296684</v>
       </c>
       <c r="R4" t="n">
-        <v>6530177</v>
+        <v>6530120</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405738</v>
+        <v>113405749</v>
       </c>
       <c r="B5" t="n">
-        <v>56766</v>
+        <v>56914</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296551</v>
+        <v>296716</v>
       </c>
       <c r="R5" t="n">
-        <v>6530280</v>
+        <v>6530077</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405744</v>
+        <v>113405747</v>
       </c>
       <c r="B6" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296637</v>
+        <v>296643</v>
       </c>
       <c r="R6" t="n">
-        <v>6530116</v>
+        <v>6530110</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405749</v>
+        <v>113405761</v>
       </c>
       <c r="B7" t="n">
-        <v>56911</v>
+        <v>96315</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296716</v>
+        <v>296536</v>
       </c>
       <c r="R7" t="n">
-        <v>6530077</v>
+        <v>6530289</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405757</v>
+        <v>113405742</v>
       </c>
       <c r="B8" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1323,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296724</v>
+        <v>296646</v>
       </c>
       <c r="R8" t="n">
-        <v>6530086</v>
+        <v>6530116</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405756</v>
+        <v>113405744</v>
       </c>
       <c r="B9" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,16 +1430,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296720</v>
+        <v>296637</v>
       </c>
       <c r="R9" t="n">
-        <v>6530093</v>
+        <v>6530116</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405742</v>
+        <v>113405739</v>
       </c>
       <c r="B10" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296646</v>
+        <v>296794</v>
       </c>
       <c r="R10" t="n">
-        <v>6530116</v>
+        <v>6530160</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,7 +1631,7 @@
         <v>113405745</v>
       </c>
       <c r="B11" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405743</v>
+        <v>113405751</v>
       </c>
       <c r="B12" t="n">
-        <v>56766</v>
+        <v>56785</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,16 +1751,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296578</v>
+        <v>296671</v>
       </c>
       <c r="R12" t="n">
-        <v>6530336</v>
+        <v>6530142</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1847,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405739</v>
+        <v>113405758</v>
       </c>
       <c r="B13" t="n">
-        <v>56766</v>
+        <v>56785</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,16 +1858,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296794</v>
+        <v>296587</v>
       </c>
       <c r="R13" t="n">
-        <v>6530160</v>
+        <v>6530221</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405741</v>
+        <v>113405750</v>
       </c>
       <c r="B14" t="n">
-        <v>56766</v>
+        <v>56785</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,16 +1965,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1994,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296641</v>
+        <v>296573</v>
       </c>
       <c r="R14" t="n">
-        <v>6530111</v>
+        <v>6530298</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2034,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405747</v>
+        <v>113405743</v>
       </c>
       <c r="B15" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296643</v>
+        <v>296578</v>
       </c>
       <c r="R15" t="n">
-        <v>6530110</v>
+        <v>6530336</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405761</v>
+        <v>113405759</v>
       </c>
       <c r="B16" t="n">
-        <v>96311</v>
+        <v>56785</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,25 +2175,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296536</v>
+        <v>296634</v>
       </c>
       <c r="R16" t="n">
-        <v>6530289</v>
+        <v>6530176</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2244,6 +2239,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405753</v>
+        <v>113405737</v>
       </c>
       <c r="B17" t="n">
-        <v>56782</v>
+        <v>93793</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296642</v>
+        <v>296703</v>
       </c>
       <c r="R17" t="n">
-        <v>6530097</v>
+        <v>6530117</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2346,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405751</v>
+        <v>113405741</v>
       </c>
       <c r="B18" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,16 +2388,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296671</v>
+        <v>296641</v>
       </c>
       <c r="R18" t="n">
-        <v>6530142</v>
+        <v>6530111</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2457,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405750</v>
+        <v>113405740</v>
       </c>
       <c r="B19" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296573</v>
+        <v>296642</v>
       </c>
       <c r="R19" t="n">
-        <v>6530298</v>
+        <v>6530112</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405759</v>
+        <v>113405754</v>
       </c>
       <c r="B20" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296634</v>
+        <v>296674</v>
       </c>
       <c r="R20" t="n">
-        <v>6530176</v>
+        <v>6530109</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2671,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405752</v>
+        <v>113405756</v>
       </c>
       <c r="B21" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296684</v>
+        <v>296720</v>
       </c>
       <c r="R21" t="n">
-        <v>6530120</v>
+        <v>6530093</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2805,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405740</v>
+        <v>113405757</v>
       </c>
       <c r="B22" t="n">
-        <v>56766</v>
+        <v>56785</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2845,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296642</v>
+        <v>296724</v>
       </c>
       <c r="R22" t="n">
-        <v>6530112</v>
+        <v>6530086</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2885,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405737</v>
+        <v>113405738</v>
       </c>
       <c r="B23" t="n">
-        <v>93789</v>
+        <v>56769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2924,25 +2919,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296703</v>
+        <v>296551</v>
       </c>
       <c r="R23" t="n">
-        <v>6530117</v>
+        <v>6530280</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2988,6 +2983,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405749</v>
+        <v>113405747</v>
       </c>
       <c r="B5" t="n">
-        <v>56914</v>
+        <v>56769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296716</v>
+        <v>296643</v>
       </c>
       <c r="R5" t="n">
-        <v>6530077</v>
+        <v>6530110</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405747</v>
+        <v>113405749</v>
       </c>
       <c r="B6" t="n">
-        <v>56769</v>
+        <v>56914</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296643</v>
+        <v>296716</v>
       </c>
       <c r="R6" t="n">
-        <v>6530110</v>
+        <v>6530077</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405737</v>
+        <v>113405741</v>
       </c>
       <c r="B17" t="n">
-        <v>93793</v>
+        <v>56769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296703</v>
+        <v>296641</v>
       </c>
       <c r="R17" t="n">
-        <v>6530117</v>
+        <v>6530111</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2346,6 +2346,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405741</v>
+        <v>113405740</v>
       </c>
       <c r="B18" t="n">
         <v>56769</v>
@@ -2412,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296641</v>
+        <v>296642</v>
       </c>
       <c r="R18" t="n">
-        <v>6530111</v>
+        <v>6530112</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2479,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405740</v>
+        <v>113405737</v>
       </c>
       <c r="B19" t="n">
-        <v>56769</v>
+        <v>93793</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,25 +2496,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296642</v>
+        <v>296703</v>
       </c>
       <c r="R19" t="n">
-        <v>6530112</v>
+        <v>6530117</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2555,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405755</v>
+        <v>113405752</v>
       </c>
       <c r="B2" t="n">
         <v>56785</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296807</v>
+        <v>296684</v>
       </c>
       <c r="R2" t="n">
-        <v>6530177</v>
+        <v>6530120</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405753</v>
+        <v>113405740</v>
       </c>
       <c r="B3" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,7 +825,7 @@
         <v>296642</v>
       </c>
       <c r="R3" t="n">
-        <v>6530097</v>
+        <v>6530112</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405752</v>
+        <v>113405756</v>
       </c>
       <c r="B4" t="n">
         <v>56785</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296684</v>
+        <v>296720</v>
       </c>
       <c r="R4" t="n">
-        <v>6530120</v>
+        <v>6530093</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405747</v>
+        <v>113405745</v>
       </c>
       <c r="B5" t="n">
         <v>56769</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296643</v>
+        <v>296589</v>
       </c>
       <c r="R5" t="n">
-        <v>6530110</v>
+        <v>6530303</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405749</v>
+        <v>113405747</v>
       </c>
       <c r="B6" t="n">
-        <v>56914</v>
+        <v>56769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296716</v>
+        <v>296643</v>
       </c>
       <c r="R6" t="n">
-        <v>6530077</v>
+        <v>6530110</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405761</v>
+        <v>113405744</v>
       </c>
       <c r="B7" t="n">
-        <v>96315</v>
+        <v>56769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296536</v>
+        <v>296637</v>
       </c>
       <c r="R7" t="n">
-        <v>6530289</v>
+        <v>6530116</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405742</v>
+        <v>113405759</v>
       </c>
       <c r="B8" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296646</v>
+        <v>296634</v>
       </c>
       <c r="R8" t="n">
-        <v>6530116</v>
+        <v>6530176</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1387,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405744</v>
+        <v>113405755</v>
       </c>
       <c r="B9" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,16 +1440,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296637</v>
+        <v>296807</v>
       </c>
       <c r="R9" t="n">
-        <v>6530116</v>
+        <v>6530177</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405739</v>
+        <v>113405757</v>
       </c>
       <c r="B10" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,16 +1547,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1561,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296794</v>
+        <v>296724</v>
       </c>
       <c r="R10" t="n">
-        <v>6530160</v>
+        <v>6530086</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1601,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405745</v>
+        <v>113405758</v>
       </c>
       <c r="B11" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,16 +1654,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1668,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296589</v>
+        <v>296587</v>
       </c>
       <c r="R11" t="n">
-        <v>6530303</v>
+        <v>6530221</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405751</v>
+        <v>113405753</v>
       </c>
       <c r="B12" t="n">
         <v>56785</v>
@@ -1775,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296671</v>
+        <v>296642</v>
       </c>
       <c r="R12" t="n">
-        <v>6530142</v>
+        <v>6530097</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1842,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405758</v>
+        <v>113405749</v>
       </c>
       <c r="B13" t="n">
-        <v>56785</v>
+        <v>56914</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296587</v>
+        <v>296716</v>
       </c>
       <c r="R13" t="n">
-        <v>6530221</v>
+        <v>6530077</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1918,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405750</v>
+        <v>113405754</v>
       </c>
       <c r="B14" t="n">
         <v>56785</v>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296573</v>
+        <v>296674</v>
       </c>
       <c r="R14" t="n">
-        <v>6530298</v>
+        <v>6530109</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2056,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405743</v>
+        <v>113405751</v>
       </c>
       <c r="B15" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,16 +2077,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2096,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296578</v>
+        <v>296671</v>
       </c>
       <c r="R15" t="n">
-        <v>6530336</v>
+        <v>6530142</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2163,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405759</v>
+        <v>113405742</v>
       </c>
       <c r="B16" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2184,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296634</v>
+        <v>296646</v>
       </c>
       <c r="R16" t="n">
-        <v>6530176</v>
+        <v>6530116</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2243,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405741</v>
+        <v>113405761</v>
       </c>
       <c r="B17" t="n">
-        <v>56769</v>
+        <v>96315</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296641</v>
+        <v>296536</v>
       </c>
       <c r="R17" t="n">
-        <v>6530111</v>
+        <v>6530289</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2346,11 +2351,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405740</v>
+        <v>113405743</v>
       </c>
       <c r="B18" t="n">
         <v>56769</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296642</v>
+        <v>296578</v>
       </c>
       <c r="R18" t="n">
-        <v>6530112</v>
+        <v>6530336</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405737</v>
+        <v>113405750</v>
       </c>
       <c r="B19" t="n">
-        <v>93793</v>
+        <v>56785</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,25 +2496,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296703</v>
+        <v>296573</v>
       </c>
       <c r="R19" t="n">
-        <v>6530117</v>
+        <v>6530298</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2560,6 +2560,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405754</v>
+        <v>113405737</v>
       </c>
       <c r="B20" t="n">
-        <v>56785</v>
+        <v>93793</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2598,25 +2603,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296674</v>
+        <v>296703</v>
       </c>
       <c r="R20" t="n">
-        <v>6530109</v>
+        <v>6530117</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2662,11 +2667,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405756</v>
+        <v>113405741</v>
       </c>
       <c r="B21" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296720</v>
+        <v>296641</v>
       </c>
       <c r="R21" t="n">
-        <v>6530093</v>
+        <v>6530111</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405757</v>
+        <v>113405738</v>
       </c>
       <c r="B22" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296724</v>
+        <v>296551</v>
       </c>
       <c r="R22" t="n">
-        <v>6530086</v>
+        <v>6530280</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405738</v>
+        <v>113405739</v>
       </c>
       <c r="B23" t="n">
         <v>56769</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296551</v>
+        <v>296794</v>
       </c>
       <c r="R23" t="n">
-        <v>6530280</v>
+        <v>6530160</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405752</v>
+        <v>113405755</v>
       </c>
       <c r="B2" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296684</v>
+        <v>296807</v>
       </c>
       <c r="R2" t="n">
-        <v>6530120</v>
+        <v>6530177</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405740</v>
+        <v>113405743</v>
       </c>
       <c r="B3" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296642</v>
+        <v>296578</v>
       </c>
       <c r="R3" t="n">
-        <v>6530112</v>
+        <v>6530336</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405756</v>
+        <v>113405757</v>
       </c>
       <c r="B4" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296720</v>
+        <v>296724</v>
       </c>
       <c r="R4" t="n">
-        <v>6530093</v>
+        <v>6530086</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405745</v>
+        <v>113405737</v>
       </c>
       <c r="B5" t="n">
-        <v>56769</v>
+        <v>93799</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296589</v>
+        <v>296703</v>
       </c>
       <c r="R5" t="n">
-        <v>6530303</v>
+        <v>6530117</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405747</v>
+        <v>113405745</v>
       </c>
       <c r="B6" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296643</v>
+        <v>296589</v>
       </c>
       <c r="R6" t="n">
-        <v>6530110</v>
+        <v>6530303</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405744</v>
+        <v>113405754</v>
       </c>
       <c r="B7" t="n">
-        <v>56769</v>
+        <v>56789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,16 +1221,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296637</v>
+        <v>296674</v>
       </c>
       <c r="R7" t="n">
-        <v>6530116</v>
+        <v>6530109</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405759</v>
+        <v>113405753</v>
       </c>
       <c r="B8" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296634</v>
+        <v>296642</v>
       </c>
       <c r="R8" t="n">
-        <v>6530176</v>
+        <v>6530097</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405755</v>
+        <v>113405759</v>
       </c>
       <c r="B9" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296807</v>
+        <v>296634</v>
       </c>
       <c r="R9" t="n">
-        <v>6530177</v>
+        <v>6530176</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405757</v>
+        <v>113405741</v>
       </c>
       <c r="B10" t="n">
-        <v>56785</v>
+        <v>56773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296724</v>
+        <v>296641</v>
       </c>
       <c r="R10" t="n">
-        <v>6530086</v>
+        <v>6530111</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405758</v>
+        <v>113405744</v>
       </c>
       <c r="B11" t="n">
-        <v>56785</v>
+        <v>56773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,16 +1649,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296587</v>
+        <v>296637</v>
       </c>
       <c r="R11" t="n">
-        <v>6530221</v>
+        <v>6530116</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405753</v>
+        <v>113405752</v>
       </c>
       <c r="B12" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296642</v>
+        <v>296684</v>
       </c>
       <c r="R12" t="n">
-        <v>6530097</v>
+        <v>6530120</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1852,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405749</v>
+        <v>113405747</v>
       </c>
       <c r="B13" t="n">
-        <v>56914</v>
+        <v>56773</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296716</v>
+        <v>296643</v>
       </c>
       <c r="R13" t="n">
-        <v>6530077</v>
+        <v>6530110</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1928,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405754</v>
+        <v>113405758</v>
       </c>
       <c r="B14" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296674</v>
+        <v>296587</v>
       </c>
       <c r="R14" t="n">
-        <v>6530109</v>
+        <v>6530221</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405751</v>
+        <v>113405756</v>
       </c>
       <c r="B15" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296671</v>
+        <v>296720</v>
       </c>
       <c r="R15" t="n">
-        <v>6530142</v>
+        <v>6530093</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405742</v>
+        <v>113405738</v>
       </c>
       <c r="B16" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296646</v>
+        <v>296551</v>
       </c>
       <c r="R16" t="n">
-        <v>6530116</v>
+        <v>6530280</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405761</v>
+        <v>113405750</v>
       </c>
       <c r="B17" t="n">
-        <v>96315</v>
+        <v>56789</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296536</v>
+        <v>296573</v>
       </c>
       <c r="R17" t="n">
-        <v>6530289</v>
+        <v>6530298</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2351,6 +2351,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405743</v>
+        <v>113405742</v>
       </c>
       <c r="B18" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296578</v>
+        <v>296646</v>
       </c>
       <c r="R18" t="n">
-        <v>6530336</v>
+        <v>6530116</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2484,10 +2489,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405750</v>
+        <v>113405751</v>
       </c>
       <c r="B19" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296573</v>
+        <v>296671</v>
       </c>
       <c r="R19" t="n">
-        <v>6530298</v>
+        <v>6530142</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2591,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405737</v>
+        <v>113405749</v>
       </c>
       <c r="B20" t="n">
-        <v>93793</v>
+        <v>56918</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2603,25 +2608,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296703</v>
+        <v>296716</v>
       </c>
       <c r="R20" t="n">
-        <v>6530117</v>
+        <v>6530077</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2693,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405741</v>
+        <v>113405739</v>
       </c>
       <c r="B21" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296641</v>
+        <v>296794</v>
       </c>
       <c r="R21" t="n">
-        <v>6530111</v>
+        <v>6530160</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2800,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405738</v>
+        <v>113405761</v>
       </c>
       <c r="B22" t="n">
-        <v>56769</v>
+        <v>96321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296551</v>
+        <v>296536</v>
       </c>
       <c r="R22" t="n">
-        <v>6530280</v>
+        <v>6530289</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2876,11 +2881,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405739</v>
+        <v>113405740</v>
       </c>
       <c r="B23" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296794</v>
+        <v>296642</v>
       </c>
       <c r="R23" t="n">
-        <v>6530160</v>
+        <v>6530112</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405755</v>
+        <v>113405756</v>
       </c>
       <c r="B2" t="n">
         <v>56789</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296807</v>
+        <v>296720</v>
       </c>
       <c r="R2" t="n">
-        <v>6530177</v>
+        <v>6530093</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405743</v>
+        <v>113405754</v>
       </c>
       <c r="B3" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296578</v>
+        <v>296674</v>
       </c>
       <c r="R3" t="n">
-        <v>6530336</v>
+        <v>6530109</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405757</v>
+        <v>113405745</v>
       </c>
       <c r="B4" t="n">
-        <v>56789</v>
+        <v>56773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296724</v>
+        <v>296589</v>
       </c>
       <c r="R4" t="n">
-        <v>6530086</v>
+        <v>6530303</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405737</v>
+        <v>113405750</v>
       </c>
       <c r="B5" t="n">
-        <v>93799</v>
+        <v>56789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296703</v>
+        <v>296573</v>
       </c>
       <c r="R5" t="n">
-        <v>6530117</v>
+        <v>6530298</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405745</v>
+        <v>113405743</v>
       </c>
       <c r="B6" t="n">
         <v>56773</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296589</v>
+        <v>296578</v>
       </c>
       <c r="R6" t="n">
-        <v>6530303</v>
+        <v>6530336</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405754</v>
+        <v>113405752</v>
       </c>
       <c r="B7" t="n">
         <v>56789</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296674</v>
+        <v>296684</v>
       </c>
       <c r="R7" t="n">
-        <v>6530109</v>
+        <v>6530120</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405753</v>
+        <v>113405749</v>
       </c>
       <c r="B8" t="n">
-        <v>56789</v>
+        <v>56918</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296642</v>
+        <v>296716</v>
       </c>
       <c r="R8" t="n">
-        <v>6530097</v>
+        <v>6530077</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405759</v>
+        <v>113405758</v>
       </c>
       <c r="B9" t="n">
         <v>56789</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296634</v>
+        <v>296587</v>
       </c>
       <c r="R9" t="n">
-        <v>6530176</v>
+        <v>6530221</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405741</v>
+        <v>113405737</v>
       </c>
       <c r="B10" t="n">
-        <v>56773</v>
+        <v>93799</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,25 +1538,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296641</v>
+        <v>296703</v>
       </c>
       <c r="R10" t="n">
-        <v>6530111</v>
+        <v>6530117</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405744</v>
+        <v>113405753</v>
       </c>
       <c r="B11" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,16 +1644,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296637</v>
+        <v>296642</v>
       </c>
       <c r="R11" t="n">
-        <v>6530116</v>
+        <v>6530097</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405752</v>
+        <v>113405751</v>
       </c>
       <c r="B12" t="n">
         <v>56789</v>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296684</v>
+        <v>296671</v>
       </c>
       <c r="R12" t="n">
-        <v>6530120</v>
+        <v>6530142</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1847,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405747</v>
+        <v>113405761</v>
       </c>
       <c r="B13" t="n">
-        <v>56773</v>
+        <v>96321</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296643</v>
+        <v>296536</v>
       </c>
       <c r="R13" t="n">
-        <v>6530110</v>
+        <v>6530289</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1923,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405758</v>
+        <v>113405747</v>
       </c>
       <c r="B14" t="n">
-        <v>56789</v>
+        <v>56773</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,16 +1960,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1994,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296587</v>
+        <v>296643</v>
       </c>
       <c r="R14" t="n">
-        <v>6530221</v>
+        <v>6530110</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2034,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405756</v>
+        <v>113405757</v>
       </c>
       <c r="B15" t="n">
         <v>56789</v>
@@ -2101,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296720</v>
+        <v>296724</v>
       </c>
       <c r="R15" t="n">
-        <v>6530093</v>
+        <v>6530086</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2168,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405738</v>
+        <v>113405741</v>
       </c>
       <c r="B16" t="n">
         <v>56773</v>
@@ -2208,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296551</v>
+        <v>296641</v>
       </c>
       <c r="R16" t="n">
-        <v>6530280</v>
+        <v>6530111</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2275,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405750</v>
+        <v>113405744</v>
       </c>
       <c r="B17" t="n">
-        <v>56789</v>
+        <v>56773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,16 +2281,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2315,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296573</v>
+        <v>296637</v>
       </c>
       <c r="R17" t="n">
-        <v>6530298</v>
+        <v>6530116</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405742</v>
+        <v>113405739</v>
       </c>
       <c r="B18" t="n">
         <v>56773</v>
@@ -2422,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296646</v>
+        <v>296794</v>
       </c>
       <c r="R18" t="n">
-        <v>6530116</v>
+        <v>6530160</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2462,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405751</v>
+        <v>113405738</v>
       </c>
       <c r="B19" t="n">
-        <v>56789</v>
+        <v>56773</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,16 +2495,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2529,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296671</v>
+        <v>296551</v>
       </c>
       <c r="R19" t="n">
-        <v>6530142</v>
+        <v>6530280</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2569,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405749</v>
+        <v>113405742</v>
       </c>
       <c r="B20" t="n">
-        <v>56918</v>
+        <v>56773</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296716</v>
+        <v>296646</v>
       </c>
       <c r="R20" t="n">
-        <v>6530077</v>
+        <v>6530116</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2672,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405739</v>
+        <v>113405755</v>
       </c>
       <c r="B21" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2714,16 +2709,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2738,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296794</v>
+        <v>296807</v>
       </c>
       <c r="R21" t="n">
-        <v>6530160</v>
+        <v>6530177</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2778,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405761</v>
+        <v>113405759</v>
       </c>
       <c r="B22" t="n">
-        <v>96321</v>
+        <v>56789</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296536</v>
+        <v>296634</v>
       </c>
       <c r="R22" t="n">
-        <v>6530289</v>
+        <v>6530176</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2881,6 +2876,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405756</v>
+        <v>113405752</v>
       </c>
       <c r="B2" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296720</v>
+        <v>296684</v>
       </c>
       <c r="R2" t="n">
-        <v>6530093</v>
+        <v>6530120</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405754</v>
+        <v>113405751</v>
       </c>
       <c r="B3" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296674</v>
+        <v>296671</v>
       </c>
       <c r="R3" t="n">
-        <v>6530109</v>
+        <v>6530142</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +892,7 @@
         <v>113405745</v>
       </c>
       <c r="B4" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405750</v>
+        <v>113405744</v>
       </c>
       <c r="B5" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296573</v>
+        <v>296637</v>
       </c>
       <c r="R5" t="n">
-        <v>6530298</v>
+        <v>6530116</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405743</v>
+        <v>113405749</v>
       </c>
       <c r="B6" t="n">
-        <v>56773</v>
+        <v>56925</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296578</v>
+        <v>296716</v>
       </c>
       <c r="R6" t="n">
-        <v>6530336</v>
+        <v>6530077</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405752</v>
+        <v>113405759</v>
       </c>
       <c r="B7" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296684</v>
+        <v>296634</v>
       </c>
       <c r="R7" t="n">
-        <v>6530120</v>
+        <v>6530176</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405749</v>
+        <v>113405747</v>
       </c>
       <c r="B8" t="n">
-        <v>56918</v>
+        <v>56780</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296716</v>
+        <v>296643</v>
       </c>
       <c r="R8" t="n">
-        <v>6530077</v>
+        <v>6530110</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405758</v>
+        <v>113405755</v>
       </c>
       <c r="B9" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296587</v>
+        <v>296807</v>
       </c>
       <c r="R9" t="n">
-        <v>6530221</v>
+        <v>6530177</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405737</v>
+        <v>113405753</v>
       </c>
       <c r="B10" t="n">
-        <v>93799</v>
+        <v>56796</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,25 +1538,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296703</v>
+        <v>296642</v>
       </c>
       <c r="R10" t="n">
-        <v>6530117</v>
+        <v>6530097</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405753</v>
+        <v>113405743</v>
       </c>
       <c r="B11" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,16 +1649,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296642</v>
+        <v>296578</v>
       </c>
       <c r="R11" t="n">
-        <v>6530097</v>
+        <v>6530336</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405751</v>
+        <v>113405740</v>
       </c>
       <c r="B12" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,16 +1756,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296671</v>
+        <v>296642</v>
       </c>
       <c r="R12" t="n">
-        <v>6530142</v>
+        <v>6530112</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405761</v>
+        <v>113405738</v>
       </c>
       <c r="B13" t="n">
-        <v>96321</v>
+        <v>56780</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1859,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296536</v>
+        <v>296551</v>
       </c>
       <c r="R13" t="n">
-        <v>6530289</v>
+        <v>6530280</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1918,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405747</v>
+        <v>113405737</v>
       </c>
       <c r="B14" t="n">
-        <v>56773</v>
+        <v>93806</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,25 +1966,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296643</v>
+        <v>296703</v>
       </c>
       <c r="R14" t="n">
-        <v>6530110</v>
+        <v>6530117</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2020,11 +2030,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405757</v>
+        <v>113405754</v>
       </c>
       <c r="B15" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296724</v>
+        <v>296674</v>
       </c>
       <c r="R15" t="n">
-        <v>6530086</v>
+        <v>6530109</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2158,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405741</v>
+        <v>113405757</v>
       </c>
       <c r="B16" t="n">
-        <v>56773</v>
+        <v>56796</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,16 +2179,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296641</v>
+        <v>296724</v>
       </c>
       <c r="R16" t="n">
-        <v>6530111</v>
+        <v>6530086</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2238,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405744</v>
+        <v>113405739</v>
       </c>
       <c r="B17" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296637</v>
+        <v>296794</v>
       </c>
       <c r="R17" t="n">
-        <v>6530116</v>
+        <v>6530160</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2345,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405739</v>
+        <v>113405756</v>
       </c>
       <c r="B18" t="n">
-        <v>56773</v>
+        <v>56796</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,16 +2393,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2412,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296794</v>
+        <v>296720</v>
       </c>
       <c r="R18" t="n">
-        <v>6530160</v>
+        <v>6530093</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405738</v>
+        <v>113405761</v>
       </c>
       <c r="B19" t="n">
-        <v>56773</v>
+        <v>96328</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,25 +2496,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296551</v>
+        <v>296536</v>
       </c>
       <c r="R19" t="n">
-        <v>6530280</v>
+        <v>6530289</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2555,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405742</v>
+        <v>113405750</v>
       </c>
       <c r="B20" t="n">
-        <v>56773</v>
+        <v>56796</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296646</v>
+        <v>296573</v>
       </c>
       <c r="R20" t="n">
-        <v>6530116</v>
+        <v>6530298</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405755</v>
+        <v>113405741</v>
       </c>
       <c r="B21" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296807</v>
+        <v>296641</v>
       </c>
       <c r="R21" t="n">
-        <v>6530177</v>
+        <v>6530111</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405759</v>
+        <v>113405758</v>
       </c>
       <c r="B22" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296634</v>
+        <v>296587</v>
       </c>
       <c r="R22" t="n">
-        <v>6530176</v>
+        <v>6530221</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405740</v>
+        <v>113405742</v>
       </c>
       <c r="B23" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296642</v>
+        <v>296646</v>
       </c>
       <c r="R23" t="n">
-        <v>6530112</v>
+        <v>6530116</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405758</v>
+        <v>113405742</v>
       </c>
       <c r="B22" t="n">
-        <v>56796</v>
+        <v>56780</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296587</v>
+        <v>296646</v>
       </c>
       <c r="R22" t="n">
-        <v>6530221</v>
+        <v>6530116</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405742</v>
+        <v>113405758</v>
       </c>
       <c r="B23" t="n">
-        <v>56780</v>
+        <v>56796</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,16 +2923,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296646</v>
+        <v>296587</v>
       </c>
       <c r="R23" t="n">
-        <v>6530116</v>
+        <v>6530221</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405742</v>
+        <v>113405758</v>
       </c>
       <c r="B22" t="n">
-        <v>56780</v>
+        <v>56796</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296646</v>
+        <v>296587</v>
       </c>
       <c r="R22" t="n">
-        <v>6530116</v>
+        <v>6530221</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405758</v>
+        <v>113405742</v>
       </c>
       <c r="B23" t="n">
-        <v>56796</v>
+        <v>56780</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,16 +2923,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296587</v>
+        <v>296646</v>
       </c>
       <c r="R23" t="n">
-        <v>6530221</v>
+        <v>6530116</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405752</v>
+        <v>113405742</v>
       </c>
       <c r="B2" t="n">
-        <v>56796</v>
+        <v>56782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296684</v>
+        <v>296646</v>
       </c>
       <c r="R2" t="n">
-        <v>6530120</v>
+        <v>6530116</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405751</v>
+        <v>113405761</v>
       </c>
       <c r="B3" t="n">
-        <v>56796</v>
+        <v>96333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296671</v>
+        <v>296536</v>
       </c>
       <c r="R3" t="n">
-        <v>6530142</v>
+        <v>6530289</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405745</v>
+        <v>113405752</v>
       </c>
       <c r="B4" t="n">
-        <v>56780</v>
+        <v>56798</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296589</v>
+        <v>296684</v>
       </c>
       <c r="R4" t="n">
-        <v>6530303</v>
+        <v>6530120</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405744</v>
+        <v>113405747</v>
       </c>
       <c r="B5" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296637</v>
+        <v>296643</v>
       </c>
       <c r="R5" t="n">
-        <v>6530116</v>
+        <v>6530110</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405749</v>
+        <v>113405738</v>
       </c>
       <c r="B6" t="n">
-        <v>56925</v>
+        <v>56782</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296716</v>
+        <v>296551</v>
       </c>
       <c r="R6" t="n">
-        <v>6530077</v>
+        <v>6530280</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405759</v>
+        <v>113405751</v>
       </c>
       <c r="B7" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296634</v>
+        <v>296671</v>
       </c>
       <c r="R7" t="n">
-        <v>6530176</v>
+        <v>6530142</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405747</v>
+        <v>113405753</v>
       </c>
       <c r="B8" t="n">
-        <v>56780</v>
+        <v>56798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296643</v>
+        <v>296642</v>
       </c>
       <c r="R8" t="n">
-        <v>6530110</v>
+        <v>6530097</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405755</v>
+        <v>113405737</v>
       </c>
       <c r="B9" t="n">
-        <v>56796</v>
+        <v>93811</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1431,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296807</v>
+        <v>296703</v>
       </c>
       <c r="R9" t="n">
-        <v>6530177</v>
+        <v>6530117</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1495,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405753</v>
+        <v>113405749</v>
       </c>
       <c r="B10" t="n">
-        <v>56796</v>
+        <v>56927</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296642</v>
+        <v>296716</v>
       </c>
       <c r="R10" t="n">
-        <v>6530097</v>
+        <v>6530077</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405743</v>
+        <v>113405739</v>
       </c>
       <c r="B11" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296578</v>
+        <v>296794</v>
       </c>
       <c r="R11" t="n">
-        <v>6530336</v>
+        <v>6530160</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1713,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405740</v>
+        <v>113405757</v>
       </c>
       <c r="B12" t="n">
-        <v>56780</v>
+        <v>56798</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,16 +1746,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1780,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296642</v>
+        <v>296724</v>
       </c>
       <c r="R12" t="n">
-        <v>6530112</v>
+        <v>6530086</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1820,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405738</v>
+        <v>113405755</v>
       </c>
       <c r="B13" t="n">
-        <v>56780</v>
+        <v>56798</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,16 +1853,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1887,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296551</v>
+        <v>296807</v>
       </c>
       <c r="R13" t="n">
-        <v>6530280</v>
+        <v>6530177</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1927,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405737</v>
+        <v>113405756</v>
       </c>
       <c r="B14" t="n">
-        <v>93806</v>
+        <v>56798</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1956,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296703</v>
+        <v>296720</v>
       </c>
       <c r="R14" t="n">
-        <v>6530117</v>
+        <v>6530093</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2030,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405754</v>
+        <v>113405758</v>
       </c>
       <c r="B15" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296674</v>
+        <v>296587</v>
       </c>
       <c r="R15" t="n">
-        <v>6530109</v>
+        <v>6530221</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405757</v>
+        <v>113405741</v>
       </c>
       <c r="B16" t="n">
-        <v>56796</v>
+        <v>56782</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,16 +2174,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296724</v>
+        <v>296641</v>
       </c>
       <c r="R16" t="n">
-        <v>6530086</v>
+        <v>6530111</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2243,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405739</v>
+        <v>113405745</v>
       </c>
       <c r="B17" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296794</v>
+        <v>296589</v>
       </c>
       <c r="R17" t="n">
-        <v>6530160</v>
+        <v>6530303</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2350,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405756</v>
+        <v>113405740</v>
       </c>
       <c r="B18" t="n">
-        <v>56796</v>
+        <v>56782</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,16 +2388,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296720</v>
+        <v>296642</v>
       </c>
       <c r="R18" t="n">
-        <v>6530093</v>
+        <v>6530112</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2457,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405761</v>
+        <v>113405750</v>
       </c>
       <c r="B19" t="n">
-        <v>96328</v>
+        <v>56798</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,25 +2491,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296536</v>
+        <v>296573</v>
       </c>
       <c r="R19" t="n">
-        <v>6530289</v>
+        <v>6530298</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2560,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405750</v>
+        <v>113405759</v>
       </c>
       <c r="B20" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296573</v>
+        <v>296634</v>
       </c>
       <c r="R20" t="n">
-        <v>6530298</v>
+        <v>6530176</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405741</v>
+        <v>113405754</v>
       </c>
       <c r="B21" t="n">
-        <v>56780</v>
+        <v>56798</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296641</v>
+        <v>296674</v>
       </c>
       <c r="R21" t="n">
-        <v>6530111</v>
+        <v>6530109</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405758</v>
+        <v>113405744</v>
       </c>
       <c r="B22" t="n">
-        <v>56796</v>
+        <v>56782</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296587</v>
+        <v>296637</v>
       </c>
       <c r="R22" t="n">
-        <v>6530221</v>
+        <v>6530116</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405742</v>
+        <v>113405743</v>
       </c>
       <c r="B23" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296646</v>
+        <v>296578</v>
       </c>
       <c r="R23" t="n">
-        <v>6530116</v>
+        <v>6530336</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405742</v>
+        <v>113405752</v>
       </c>
       <c r="B2" t="n">
-        <v>56782</v>
+        <v>56798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296646</v>
+        <v>296684</v>
       </c>
       <c r="R2" t="n">
-        <v>6530116</v>
+        <v>6530120</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405761</v>
+        <v>113405742</v>
       </c>
       <c r="B3" t="n">
-        <v>96333</v>
+        <v>56782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296536</v>
+        <v>296646</v>
       </c>
       <c r="R3" t="n">
-        <v>6530289</v>
+        <v>6530116</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405752</v>
+        <v>113405761</v>
       </c>
       <c r="B4" t="n">
-        <v>56798</v>
+        <v>96333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296684</v>
+        <v>296536</v>
       </c>
       <c r="R4" t="n">
-        <v>6530120</v>
+        <v>6530289</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405756</v>
+        <v>113405758</v>
       </c>
       <c r="B14" t="n">
         <v>56798</v>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296720</v>
+        <v>296587</v>
       </c>
       <c r="R14" t="n">
-        <v>6530093</v>
+        <v>6530221</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405758</v>
+        <v>113405741</v>
       </c>
       <c r="B15" t="n">
-        <v>56798</v>
+        <v>56782</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,16 +2067,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296587</v>
+        <v>296641</v>
       </c>
       <c r="R15" t="n">
-        <v>6530221</v>
+        <v>6530111</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405741</v>
+        <v>113405756</v>
       </c>
       <c r="B16" t="n">
-        <v>56782</v>
+        <v>56798</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296641</v>
+        <v>296720</v>
       </c>
       <c r="R16" t="n">
-        <v>6530111</v>
+        <v>6530093</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405752</v>
+        <v>113405757</v>
       </c>
       <c r="B2" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296684</v>
+        <v>296724</v>
       </c>
       <c r="R2" t="n">
-        <v>6530120</v>
+        <v>6530086</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405742</v>
+        <v>113405759</v>
       </c>
       <c r="B3" t="n">
-        <v>56782</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296646</v>
+        <v>296634</v>
       </c>
       <c r="R3" t="n">
-        <v>6530116</v>
+        <v>6530176</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405761</v>
+        <v>113405750</v>
       </c>
       <c r="B4" t="n">
-        <v>96333</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296536</v>
+        <v>296573</v>
       </c>
       <c r="R4" t="n">
-        <v>6530289</v>
+        <v>6530298</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405747</v>
+        <v>113405742</v>
       </c>
       <c r="B5" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296643</v>
+        <v>296646</v>
       </c>
       <c r="R5" t="n">
-        <v>6530110</v>
+        <v>6530116</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405738</v>
+        <v>113405758</v>
       </c>
       <c r="B6" t="n">
-        <v>56782</v>
+        <v>56826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296551</v>
+        <v>296587</v>
       </c>
       <c r="R6" t="n">
-        <v>6530280</v>
+        <v>6530221</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405751</v>
+        <v>113405740</v>
       </c>
       <c r="B7" t="n">
-        <v>56798</v>
+        <v>56810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,16 +1226,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296671</v>
+        <v>296642</v>
       </c>
       <c r="R7" t="n">
-        <v>6530142</v>
+        <v>6530112</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405753</v>
+        <v>113405745</v>
       </c>
       <c r="B8" t="n">
-        <v>56798</v>
+        <v>56810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1333,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296642</v>
+        <v>296589</v>
       </c>
       <c r="R8" t="n">
-        <v>6530097</v>
+        <v>6530303</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405737</v>
+        <v>113405761</v>
       </c>
       <c r="B9" t="n">
-        <v>93811</v>
+        <v>96361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296703</v>
+        <v>296536</v>
       </c>
       <c r="R9" t="n">
-        <v>6530117</v>
+        <v>6530289</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405749</v>
+        <v>113405756</v>
       </c>
       <c r="B10" t="n">
-        <v>56927</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296716</v>
+        <v>296720</v>
       </c>
       <c r="R10" t="n">
-        <v>6530077</v>
+        <v>6530093</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405739</v>
+        <v>113405738</v>
       </c>
       <c r="B11" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296794</v>
+        <v>296551</v>
       </c>
       <c r="R11" t="n">
-        <v>6530160</v>
+        <v>6530280</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1730,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405757</v>
+        <v>113405737</v>
       </c>
       <c r="B12" t="n">
-        <v>56798</v>
+        <v>93839</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296724</v>
+        <v>296703</v>
       </c>
       <c r="R12" t="n">
-        <v>6530086</v>
+        <v>6530117</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405755</v>
+        <v>113405741</v>
       </c>
       <c r="B13" t="n">
-        <v>56798</v>
+        <v>56810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,16 +1858,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296807</v>
+        <v>296641</v>
       </c>
       <c r="R13" t="n">
-        <v>6530177</v>
+        <v>6530111</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1917,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405758</v>
+        <v>113405755</v>
       </c>
       <c r="B14" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296587</v>
+        <v>296807</v>
       </c>
       <c r="R14" t="n">
-        <v>6530221</v>
+        <v>6530177</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2051,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405741</v>
+        <v>113405753</v>
       </c>
       <c r="B15" t="n">
-        <v>56782</v>
+        <v>56826</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,16 +2072,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296641</v>
+        <v>296642</v>
       </c>
       <c r="R15" t="n">
-        <v>6530111</v>
+        <v>6530097</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2131,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405756</v>
+        <v>113405749</v>
       </c>
       <c r="B16" t="n">
-        <v>56798</v>
+        <v>56955</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296720</v>
+        <v>296716</v>
       </c>
       <c r="R16" t="n">
-        <v>6530093</v>
+        <v>6530077</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2234,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405745</v>
+        <v>113405752</v>
       </c>
       <c r="B17" t="n">
-        <v>56782</v>
+        <v>56826</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296589</v>
+        <v>296684</v>
       </c>
       <c r="R17" t="n">
-        <v>6530303</v>
+        <v>6530120</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405740</v>
+        <v>113405751</v>
       </c>
       <c r="B18" t="n">
-        <v>56782</v>
+        <v>56826</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,16 +2388,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296642</v>
+        <v>296671</v>
       </c>
       <c r="R18" t="n">
-        <v>6530112</v>
+        <v>6530142</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405750</v>
+        <v>113405754</v>
       </c>
       <c r="B19" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296573</v>
+        <v>296674</v>
       </c>
       <c r="R19" t="n">
-        <v>6530298</v>
+        <v>6530109</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405759</v>
+        <v>113405744</v>
       </c>
       <c r="B20" t="n">
-        <v>56798</v>
+        <v>56810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,16 +2602,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296634</v>
+        <v>296637</v>
       </c>
       <c r="R20" t="n">
-        <v>6530176</v>
+        <v>6530116</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405754</v>
+        <v>113405747</v>
       </c>
       <c r="B21" t="n">
-        <v>56798</v>
+        <v>56810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296674</v>
+        <v>296643</v>
       </c>
       <c r="R21" t="n">
-        <v>6530109</v>
+        <v>6530110</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405744</v>
+        <v>113405739</v>
       </c>
       <c r="B22" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296637</v>
+        <v>296794</v>
       </c>
       <c r="R22" t="n">
-        <v>6530116</v>
+        <v>6530160</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,7 +2910,7 @@
         <v>113405743</v>
       </c>
       <c r="B23" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405757</v>
+        <v>113405759</v>
       </c>
       <c r="B2" t="n">
         <v>56826</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296724</v>
+        <v>296634</v>
       </c>
       <c r="R2" t="n">
-        <v>6530086</v>
+        <v>6530176</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405759</v>
+        <v>113405742</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>56810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296634</v>
+        <v>296646</v>
       </c>
       <c r="R3" t="n">
-        <v>6530176</v>
+        <v>6530116</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113405750</v>
+        <v>113405751</v>
       </c>
       <c r="B4" t="n">
         <v>56826</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296573</v>
+        <v>296671</v>
       </c>
       <c r="R4" t="n">
-        <v>6530298</v>
+        <v>6530142</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405742</v>
+        <v>113405756</v>
       </c>
       <c r="B5" t="n">
-        <v>56810</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296646</v>
+        <v>296720</v>
       </c>
       <c r="R5" t="n">
-        <v>6530116</v>
+        <v>6530093</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405758</v>
+        <v>113405754</v>
       </c>
       <c r="B6" t="n">
         <v>56826</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296587</v>
+        <v>296674</v>
       </c>
       <c r="R6" t="n">
-        <v>6530221</v>
+        <v>6530109</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405740</v>
+        <v>113405743</v>
       </c>
       <c r="B7" t="n">
         <v>56810</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296642</v>
+        <v>296578</v>
       </c>
       <c r="R7" t="n">
-        <v>6530112</v>
+        <v>6530336</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405745</v>
+        <v>113405749</v>
       </c>
       <c r="B8" t="n">
-        <v>56810</v>
+        <v>56955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296589</v>
+        <v>296716</v>
       </c>
       <c r="R8" t="n">
-        <v>6530303</v>
+        <v>6530077</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1393,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405761</v>
+        <v>113405738</v>
       </c>
       <c r="B9" t="n">
-        <v>96361</v>
+        <v>56810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,25 +1431,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296536</v>
+        <v>296551</v>
       </c>
       <c r="R9" t="n">
-        <v>6530289</v>
+        <v>6530280</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405756</v>
+        <v>113405740</v>
       </c>
       <c r="B10" t="n">
-        <v>56826</v>
+        <v>56810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296720</v>
+        <v>296642</v>
       </c>
       <c r="R10" t="n">
-        <v>6530093</v>
+        <v>6530112</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405738</v>
+        <v>113405761</v>
       </c>
       <c r="B11" t="n">
-        <v>56810</v>
+        <v>96361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296551</v>
+        <v>296536</v>
       </c>
       <c r="R11" t="n">
-        <v>6530280</v>
+        <v>6530289</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405737</v>
+        <v>113405747</v>
       </c>
       <c r="B12" t="n">
-        <v>93839</v>
+        <v>56810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296703</v>
+        <v>296643</v>
       </c>
       <c r="R12" t="n">
-        <v>6530117</v>
+        <v>6530110</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1816,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405741</v>
+        <v>113405757</v>
       </c>
       <c r="B13" t="n">
-        <v>56810</v>
+        <v>56826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296641</v>
+        <v>296724</v>
       </c>
       <c r="R13" t="n">
-        <v>6530111</v>
+        <v>6530086</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405753</v>
+        <v>113405758</v>
       </c>
       <c r="B15" t="n">
         <v>56826</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296642</v>
+        <v>296587</v>
       </c>
       <c r="R15" t="n">
-        <v>6530097</v>
+        <v>6530221</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405749</v>
+        <v>113405750</v>
       </c>
       <c r="B16" t="n">
-        <v>56955</v>
+        <v>56826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296716</v>
+        <v>296573</v>
       </c>
       <c r="R16" t="n">
-        <v>6530077</v>
+        <v>6530298</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2239,6 +2239,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405752</v>
+        <v>113405744</v>
       </c>
       <c r="B17" t="n">
-        <v>56826</v>
+        <v>56810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,16 +2286,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2305,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296684</v>
+        <v>296637</v>
       </c>
       <c r="R17" t="n">
-        <v>6530120</v>
+        <v>6530116</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2345,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405751</v>
+        <v>113405745</v>
       </c>
       <c r="B18" t="n">
-        <v>56826</v>
+        <v>56810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,16 +2393,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2412,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296671</v>
+        <v>296589</v>
       </c>
       <c r="R18" t="n">
-        <v>6530142</v>
+        <v>6530303</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2452,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405754</v>
+        <v>113405752</v>
       </c>
       <c r="B19" t="n">
         <v>56826</v>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296674</v>
+        <v>296684</v>
       </c>
       <c r="R19" t="n">
-        <v>6530109</v>
+        <v>6530120</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2586,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113405744</v>
+        <v>113405753</v>
       </c>
       <c r="B20" t="n">
-        <v>56810</v>
+        <v>56826</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,16 +2607,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2626,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>296637</v>
+        <v>296642</v>
       </c>
       <c r="R20" t="n">
-        <v>6530116</v>
+        <v>6530097</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2666,7 +2671,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405747</v>
+        <v>113405741</v>
       </c>
       <c r="B21" t="n">
         <v>56810</v>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296643</v>
+        <v>296641</v>
       </c>
       <c r="R21" t="n">
-        <v>6530110</v>
+        <v>6530111</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2773,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2907,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405743</v>
+        <v>113405737</v>
       </c>
       <c r="B23" t="n">
-        <v>56810</v>
+        <v>93839</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,25 +2924,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296578</v>
+        <v>296703</v>
       </c>
       <c r="R23" t="n">
-        <v>6530336</v>
+        <v>6530117</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2983,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121783269</v>
+        <v>121783254</v>
       </c>
       <c r="B24" t="n">
         <v>56569</v>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>296769</v>
+        <v>296738</v>
       </c>
       <c r="R24" t="n">
-        <v>6530117</v>
+        <v>6530153</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121783254</v>
+        <v>121783269</v>
       </c>
       <c r="B25" t="n">
         <v>56569</v>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>296738</v>
+        <v>296769</v>
       </c>
       <c r="R25" t="n">
-        <v>6530153</v>
+        <v>6530117</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121783254</v>
+        <v>121783269</v>
       </c>
       <c r="B24" t="n">
         <v>56569</v>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>296738</v>
+        <v>296769</v>
       </c>
       <c r="R24" t="n">
-        <v>6530153</v>
+        <v>6530117</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121783269</v>
+        <v>121783254</v>
       </c>
       <c r="B25" t="n">
         <v>56569</v>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>296769</v>
+        <v>296738</v>
       </c>
       <c r="R25" t="n">
-        <v>6530117</v>
+        <v>6530153</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3014,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121783254</v>
+        <v>121783269</v>
       </c>
       <c r="B24" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>296738</v>
+        <v>296769</v>
       </c>
       <c r="R24" t="n">
-        <v>6530153</v>
+        <v>6530117</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121783269</v>
+        <v>121783254</v>
       </c>
       <c r="B25" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>296769</v>
+        <v>296738</v>
       </c>
       <c r="R25" t="n">
-        <v>6530117</v>
+        <v>6530153</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121783269</v>
+        <v>121783254</v>
       </c>
       <c r="B24" t="n">
         <v>56577</v>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>296769</v>
+        <v>296738</v>
       </c>
       <c r="R24" t="n">
-        <v>6530117</v>
+        <v>6530153</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121783254</v>
+        <v>121783269</v>
       </c>
       <c r="B25" t="n">
         <v>56577</v>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>296738</v>
+        <v>296769</v>
       </c>
       <c r="R25" t="n">
-        <v>6530153</v>
+        <v>6530117</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3231,6 +3231,121 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122106110</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 12671-2023, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>296545</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6530285</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre och ganska rikligt i äldre tall.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>122106110</v>
       </c>
       <c r="B26" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3252,11 +3252,6 @@
       <c r="E26" t="n">
         <v>100109</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>122106110</v>
       </c>
       <c r="B26" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,6 +3251,11 @@
       </c>
       <c r="E26" t="n">
         <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3017,11 +3017,11 @@
         <v>121783254</v>
       </c>
       <c r="B24" t="n">
-        <v>56584</v>
+        <v>56594</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3127,11 +3127,11 @@
         <v>121783269</v>
       </c>
       <c r="B25" t="n">
-        <v>56584</v>
+        <v>56594</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3017,7 +3017,7 @@
         <v>121783254</v>
       </c>
       <c r="B24" t="n">
-        <v>56594</v>
+        <v>56688</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>121783269</v>
       </c>
       <c r="B25" t="n">
-        <v>56594</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3017,7 +3017,7 @@
         <v>121783254</v>
       </c>
       <c r="B24" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>121783269</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3017,7 +3017,7 @@
         <v>121783254</v>
       </c>
       <c r="B24" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>121783269</v>
       </c>
       <c r="B25" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3017,7 +3017,7 @@
         <v>121783254</v>
       </c>
       <c r="B24" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>121783269</v>
       </c>
       <c r="B25" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>122106110</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
+        <v>57491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113405759</v>
+        <v>113405737</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296635</v>
+        <v>296703</v>
       </c>
       <c r="R2" t="n">
-        <v>6530176</v>
+        <v>6530117</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113405758</v>
+        <v>113405750</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296587</v>
+        <v>296573</v>
       </c>
       <c r="R3" t="n">
-        <v>6530222</v>
+        <v>6530299</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,16 +877,11 @@
         <v>113405751</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -996,32 +976,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113405742</v>
+        <v>113405752</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1036,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296646</v>
+        <v>296684</v>
       </c>
       <c r="R5" t="n">
-        <v>6530116</v>
+        <v>6530120</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,32 +1078,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113405741</v>
+        <v>113405753</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1146,7 +1116,7 @@
         <v>296641</v>
       </c>
       <c r="R6" t="n">
-        <v>6530111</v>
+        <v>6530098</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1153,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,19 +1180,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113405752</v>
+        <v>113405754</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296684</v>
+        <v>296674</v>
       </c>
       <c r="R7" t="n">
-        <v>6530120</v>
+        <v>6530110</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1317,32 +1282,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113405739</v>
+        <v>113405755</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1357,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296794</v>
+        <v>296807</v>
       </c>
       <c r="R8" t="n">
-        <v>6530160</v>
+        <v>6530177</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,7 +1357,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1384,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113405738</v>
+        <v>113405756</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1464,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>296550</v>
+        <v>296720</v>
       </c>
       <c r="R9" t="n">
-        <v>6530280</v>
+        <v>6530093</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1504,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1486,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113405740</v>
+        <v>113405757</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1571,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>296642</v>
+        <v>296724</v>
       </c>
       <c r="R10" t="n">
-        <v>6530112</v>
+        <v>6530086</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1611,7 +1561,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1588,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113405743</v>
+        <v>113405758</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1678,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>296578</v>
+        <v>296587</v>
       </c>
       <c r="R11" t="n">
-        <v>6530337</v>
+        <v>6530222</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1745,19 +1690,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113405756</v>
+        <v>113405759</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1785,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>296720</v>
+        <v>296635</v>
       </c>
       <c r="R12" t="n">
-        <v>6530093</v>
+        <v>6530176</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1825,7 +1765,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,15 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113405761</v>
+        <v>113405760</v>
       </c>
       <c r="B13" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1803,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>296536</v>
+        <v>296515</v>
       </c>
       <c r="R13" t="n">
-        <v>6530289</v>
+        <v>6530311</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1928,6 +1863,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,15 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113405757</v>
+        <v>113405738</v>
       </c>
       <c r="B14" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,16 +1905,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1994,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>296724</v>
+        <v>296550</v>
       </c>
       <c r="R14" t="n">
-        <v>6530086</v>
+        <v>6530280</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2034,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,37 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113405737</v>
+        <v>113405739</v>
       </c>
       <c r="B15" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>296703</v>
+        <v>296794</v>
       </c>
       <c r="R15" t="n">
-        <v>6530117</v>
+        <v>6530160</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2137,6 +2067,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,15 +2098,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113405745</v>
+        <v>113405740</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>296589</v>
+        <v>296642</v>
       </c>
       <c r="R16" t="n">
-        <v>6530302</v>
+        <v>6530112</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2243,7 +2173,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska hack högt upp utefter tallstammen</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,15 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113405747</v>
+        <v>113405741</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>296643</v>
+        <v>296641</v>
       </c>
       <c r="R17" t="n">
-        <v>6530109</v>
+        <v>6530111</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2350,7 +2275,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,15 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113405754</v>
+        <v>113405742</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,16 +2313,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2417,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>296674</v>
+        <v>296646</v>
       </c>
       <c r="R18" t="n">
-        <v>6530110</v>
+        <v>6530116</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2484,15 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113405750</v>
+        <v>113405743</v>
       </c>
       <c r="B19" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,16 +2415,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2524,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>296573</v>
+        <v>296578</v>
       </c>
       <c r="R19" t="n">
-        <v>6530299</v>
+        <v>6530337</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2594,12 +2509,7 @@
         <v>113405744</v>
       </c>
       <c r="B20" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2698,15 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113405753</v>
+        <v>113405745</v>
       </c>
       <c r="B21" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,16 +2619,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2738,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>296641</v>
+        <v>296589</v>
       </c>
       <c r="R21" t="n">
-        <v>6530098</v>
+        <v>6530302</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2778,7 +2683,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack högt upp utefter tallstammen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,15 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113405755</v>
+        <v>113405747</v>
       </c>
       <c r="B22" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,16 +2721,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2845,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>296807</v>
+        <v>296643</v>
       </c>
       <c r="R22" t="n">
-        <v>6530177</v>
+        <v>6530109</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2885,7 +2785,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,15 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113405749</v>
+        <v>122106110</v>
       </c>
       <c r="B23" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,37 +2823,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blötevattnet, Boh</t>
+          <t>A 12671-2023, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>296715</v>
+        <v>296545</v>
       </c>
       <c r="R23" t="n">
-        <v>6530077</v>
+        <v>6530285</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,12 +2885,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre och ganska rikligt i äldre tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3002,12 +2910,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3017,12 +2925,7 @@
         <v>121783254</v>
       </c>
       <c r="B24" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3127,12 +3030,7 @@
         <v>121783269</v>
       </c>
       <c r="B25" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,61 +3132,59 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122106110</v>
+        <v>86043575</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>102118</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 12671-2023, Boh</t>
+          <t>S Blötevattnet , Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>296545</v>
+        <v>296554</v>
       </c>
       <c r="R26" t="n">
-        <v>6530285</v>
+        <v>6530176</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3312,17 +3208,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre och ganska rikligt i äldre tall.</t>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3337,15 +3238,209 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Per Toräng</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Per Toräng</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113405749</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Blötevattnet, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>296715</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6530077</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113405761</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Blötevattnet, Boh</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>296536</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6530289</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12671-2023 artfynd.xlsx
+++ b/artfynd/A 12671-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405737</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405750</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405751</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405752</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405753</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405754</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405755</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405756</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405757</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405758</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405759</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405760</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405738</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405739</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405740</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405741</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405742</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2503,6 +2593,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405743</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405744</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2707,6 +2807,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405745</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405747</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2919,6 +3029,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122106110</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3024,6 +3139,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121783254</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121783269</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3247,6 +3372,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86043575</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3344,6 +3474,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405749</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3441,8 +3576,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113405761</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>